--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131451</v>
+        <v>122131450</v>
       </c>
       <c r="B2" t="n">
-        <v>97094</v>
+        <v>90754</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559636</v>
+        <v>559608</v>
       </c>
       <c r="R2" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131455</v>
+        <v>122131454</v>
       </c>
       <c r="B3" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559606</v>
+        <v>559592</v>
       </c>
       <c r="R3" t="n">
-        <v>7111626</v>
+        <v>7111622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122131452</v>
       </c>
       <c r="B4" t="n">
-        <v>97094</v>
+        <v>97103</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131454</v>
+        <v>122131451</v>
       </c>
       <c r="B5" t="n">
-        <v>90745</v>
+        <v>97103</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559592</v>
+        <v>559636</v>
       </c>
       <c r="R5" t="n">
-        <v>7111622</v>
+        <v>7111639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131450</v>
+        <v>122131455</v>
       </c>
       <c r="B6" t="n">
-        <v>90745</v>
+        <v>90754</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559608</v>
+        <v>559606</v>
       </c>
       <c r="R6" t="n">
-        <v>7111621</v>
+        <v>7111626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131452</v>
+        <v>122131451</v>
       </c>
       <c r="B2" t="n">
         <v>97129</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559591</v>
+        <v>559636</v>
       </c>
       <c r="R2" t="n">
-        <v>7111621</v>
+        <v>7111639</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131451</v>
+        <v>122131450</v>
       </c>
       <c r="B3" t="n">
-        <v>97129</v>
+        <v>90779</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559636</v>
+        <v>559608</v>
       </c>
       <c r="R3" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131450</v>
+        <v>122131455</v>
       </c>
       <c r="B4" t="n">
         <v>90779</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559608</v>
+        <v>559606</v>
       </c>
       <c r="R4" t="n">
-        <v>7111621</v>
+        <v>7111626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131455</v>
+        <v>122131454</v>
       </c>
       <c r="B5" t="n">
         <v>90779</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559606</v>
+        <v>559592</v>
       </c>
       <c r="R5" t="n">
-        <v>7111626</v>
+        <v>7111622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131454</v>
+        <v>122131452</v>
       </c>
       <c r="B6" t="n">
-        <v>90779</v>
+        <v>97129</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559592</v>
+        <v>559591</v>
       </c>
       <c r="R6" t="n">
-        <v>7111622</v>
+        <v>7111621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131451</v>
+        <v>122131450</v>
       </c>
       <c r="B2" t="n">
-        <v>97129</v>
+        <v>90789</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559636</v>
+        <v>559608</v>
       </c>
       <c r="R2" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131450</v>
+        <v>122131455</v>
       </c>
       <c r="B3" t="n">
-        <v>90779</v>
+        <v>90789</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559608</v>
+        <v>559606</v>
       </c>
       <c r="R3" t="n">
-        <v>7111621</v>
+        <v>7111626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131455</v>
+        <v>122131452</v>
       </c>
       <c r="B4" t="n">
-        <v>90779</v>
+        <v>97139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559606</v>
+        <v>559591</v>
       </c>
       <c r="R4" t="n">
-        <v>7111626</v>
+        <v>7111621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131454</v>
+        <v>122131451</v>
       </c>
       <c r="B5" t="n">
-        <v>90779</v>
+        <v>97139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559592</v>
+        <v>559636</v>
       </c>
       <c r="R5" t="n">
-        <v>7111622</v>
+        <v>7111639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131452</v>
+        <v>122131454</v>
       </c>
       <c r="B6" t="n">
-        <v>97129</v>
+        <v>90789</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559591</v>
+        <v>559592</v>
       </c>
       <c r="R6" t="n">
-        <v>7111621</v>
+        <v>7111622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131455</v>
+        <v>122131451</v>
       </c>
       <c r="B3" t="n">
-        <v>90789</v>
+        <v>97139</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559606</v>
+        <v>559636</v>
       </c>
       <c r="R3" t="n">
-        <v>7111626</v>
+        <v>7111639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131451</v>
+        <v>122131454</v>
       </c>
       <c r="B5" t="n">
-        <v>97139</v>
+        <v>90789</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559636</v>
+        <v>559592</v>
       </c>
       <c r="R5" t="n">
-        <v>7111639</v>
+        <v>7111622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131454</v>
+        <v>122131455</v>
       </c>
       <c r="B6" t="n">
         <v>90789</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559592</v>
+        <v>559606</v>
       </c>
       <c r="R6" t="n">
-        <v>7111622</v>
+        <v>7111626</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131450</v>
+        <v>122131455</v>
       </c>
       <c r="B2" t="n">
-        <v>90789</v>
+        <v>90801</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559608</v>
+        <v>559606</v>
       </c>
       <c r="R2" t="n">
-        <v>7111621</v>
+        <v>7111626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131451</v>
+        <v>122131454</v>
       </c>
       <c r="B3" t="n">
-        <v>97139</v>
+        <v>90801</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559636</v>
+        <v>559592</v>
       </c>
       <c r="R3" t="n">
-        <v>7111639</v>
+        <v>7111622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,7 +882,7 @@
         <v>122131452</v>
       </c>
       <c r="B4" t="n">
-        <v>97139</v>
+        <v>97151</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131454</v>
+        <v>122131450</v>
       </c>
       <c r="B5" t="n">
-        <v>90789</v>
+        <v>90801</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559592</v>
+        <v>559608</v>
       </c>
       <c r="R5" t="n">
-        <v>7111622</v>
+        <v>7111621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131455</v>
+        <v>122131451</v>
       </c>
       <c r="B6" t="n">
-        <v>90789</v>
+        <v>97151</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559606</v>
+        <v>559636</v>
       </c>
       <c r="R6" t="n">
-        <v>7111626</v>
+        <v>7111639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131455</v>
+        <v>122131450</v>
       </c>
       <c r="B2" t="n">
-        <v>90801</v>
+        <v>90808</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559606</v>
+        <v>559608</v>
       </c>
       <c r="R2" t="n">
-        <v>7111626</v>
+        <v>7111621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131454</v>
+        <v>122131455</v>
       </c>
       <c r="B3" t="n">
-        <v>90801</v>
+        <v>90808</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559592</v>
+        <v>559606</v>
       </c>
       <c r="R3" t="n">
-        <v>7111622</v>
+        <v>7111626</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131452</v>
+        <v>122131451</v>
       </c>
       <c r="B4" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559591</v>
+        <v>559636</v>
       </c>
       <c r="R4" t="n">
-        <v>7111621</v>
+        <v>7111639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131450</v>
+        <v>122131454</v>
       </c>
       <c r="B5" t="n">
-        <v>90801</v>
+        <v>90808</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559608</v>
+        <v>559592</v>
       </c>
       <c r="R5" t="n">
-        <v>7111621</v>
+        <v>7111622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131451</v>
+        <v>122131452</v>
       </c>
       <c r="B6" t="n">
-        <v>97151</v>
+        <v>97156</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559636</v>
+        <v>559591</v>
       </c>
       <c r="R6" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131450</v>
+        <v>122131452</v>
       </c>
       <c r="B2" t="n">
-        <v>90808</v>
+        <v>97165</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +710,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559608</v>
+        <v>559591</v>
       </c>
       <c r="R2" t="n">
         <v>7111621</v>
@@ -780,7 +775,7 @@
         <v>122131455</v>
       </c>
       <c r="B3" t="n">
-        <v>90808</v>
+        <v>90813</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -794,11 +789,6 @@
       </c>
       <c r="E3" t="n">
         <v>1202</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -879,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131451</v>
+        <v>122131450</v>
       </c>
       <c r="B4" t="n">
-        <v>97156</v>
+        <v>90813</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +881,20 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559636</v>
+        <v>559608</v>
       </c>
       <c r="R4" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131454</v>
+        <v>122131451</v>
       </c>
       <c r="B5" t="n">
-        <v>90808</v>
+        <v>97165</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +978,20 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559592</v>
+        <v>559636</v>
       </c>
       <c r="R5" t="n">
-        <v>7111622</v>
+        <v>7111639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131452</v>
+        <v>122131454</v>
       </c>
       <c r="B6" t="n">
-        <v>97156</v>
+        <v>90813</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1075,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>1202</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559591</v>
+        <v>559592</v>
       </c>
       <c r="R6" t="n">
-        <v>7111621</v>
+        <v>7111622</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131452</v>
+        <v>122131455</v>
       </c>
       <c r="B2" t="n">
-        <v>97165</v>
+        <v>90826</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>1202</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559591</v>
+        <v>559606</v>
       </c>
       <c r="R2" t="n">
-        <v>7111621</v>
+        <v>7111626</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131455</v>
+        <v>122131454</v>
       </c>
       <c r="B3" t="n">
-        <v>90813</v>
+        <v>90826</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -790,6 +795,11 @@
       <c r="E3" t="n">
         <v>1202</v>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
       <c r="G3" t="inlineStr">
         <is>
           <t>Phellinidium ferrugineofuscum</t>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559606</v>
+        <v>559592</v>
       </c>
       <c r="R3" t="n">
-        <v>7111626</v>
+        <v>7111622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131450</v>
+        <v>122131451</v>
       </c>
       <c r="B4" t="n">
-        <v>90813</v>
+        <v>97178</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -881,20 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559608</v>
+        <v>559636</v>
       </c>
       <c r="R4" t="n">
-        <v>7111621</v>
+        <v>7111639</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131451</v>
+        <v>122131450</v>
       </c>
       <c r="B5" t="n">
-        <v>97165</v>
+        <v>90826</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -978,20 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559636</v>
+        <v>559608</v>
       </c>
       <c r="R5" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131454</v>
+        <v>122131452</v>
       </c>
       <c r="B6" t="n">
-        <v>90813</v>
+        <v>97178</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1075,20 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559592</v>
+        <v>559591</v>
       </c>
       <c r="R6" t="n">
-        <v>7111622</v>
+        <v>7111621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122131455</v>
       </c>
       <c r="B2" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131454</v>
+        <v>122131452</v>
       </c>
       <c r="B3" t="n">
-        <v>90826</v>
+        <v>97191</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559592</v>
+        <v>559591</v>
       </c>
       <c r="R3" t="n">
-        <v>7111622</v>
+        <v>7111621</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131451</v>
+        <v>122131450</v>
       </c>
       <c r="B4" t="n">
-        <v>97178</v>
+        <v>90839</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559636</v>
+        <v>559608</v>
       </c>
       <c r="R4" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131450</v>
+        <v>122131454</v>
       </c>
       <c r="B5" t="n">
-        <v>90826</v>
+        <v>90839</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559608</v>
+        <v>559592</v>
       </c>
       <c r="R5" t="n">
-        <v>7111621</v>
+        <v>7111622</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131452</v>
+        <v>122131451</v>
       </c>
       <c r="B6" t="n">
-        <v>97178</v>
+        <v>97191</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559591</v>
+        <v>559636</v>
       </c>
       <c r="R6" t="n">
-        <v>7111621</v>
+        <v>7111639</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122131455</v>
+        <v>122131450</v>
       </c>
       <c r="B2" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>559606</v>
+        <v>559608</v>
       </c>
       <c r="R2" t="n">
-        <v>7111626</v>
+        <v>7111621</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122131452</v>
+        <v>122131454</v>
       </c>
       <c r="B3" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>559591</v>
+        <v>559592</v>
       </c>
       <c r="R3" t="n">
-        <v>7111621</v>
+        <v>7111622</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122131450</v>
+        <v>122131455</v>
       </c>
       <c r="B4" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>559608</v>
+        <v>559606</v>
       </c>
       <c r="R4" t="n">
-        <v>7111621</v>
+        <v>7111626</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122131454</v>
+        <v>122131451</v>
       </c>
       <c r="B5" t="n">
-        <v>90839</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>559592</v>
+        <v>559636</v>
       </c>
       <c r="R5" t="n">
-        <v>7111622</v>
+        <v>7111639</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,15 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122131451</v>
+        <v>122131452</v>
       </c>
       <c r="B6" t="n">
-        <v>97191</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>559636</v>
+        <v>559591</v>
       </c>
       <c r="R6" t="n">
-        <v>7111639</v>
+        <v>7111621</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 49183-2024 artfynd.xlsx
+++ b/artfynd/A 49183-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131450</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131454</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131455</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131451</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,8 +1182,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122131452</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>